--- a/artfynd/A 50106-2023 artfynd.xlsx
+++ b/artfynd/A 50106-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,6 +775,217 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>114726255</v>
+      </c>
+      <c r="B3" t="n">
+        <v>104614</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Holklinjen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>469233</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6547512</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114726489</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56446</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Holklinjen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>469233</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6547512</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50106-2023 artfynd.xlsx
+++ b/artfynd/A 50106-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
